--- a/Input/Q and Meteo/Meteo_Daily.xlsx
+++ b/Input/Q and Meteo/Meteo_Daily.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10512"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/audreycampeau/Documents/DATA/TROLLBERGET DITCH/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/audreycampeau/Documents/DATA/TROLLBERGET DITCH/R/Input/Q and Meteo/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{022EC247-058F-5247-885E-DD5AEC0DDE38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A15978B-834A-4240-92B0-221923B1E78F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="720" yWindow="1820" windowWidth="27640" windowHeight="16940" xr2:uid="{54D7949B-B9B2-C347-8E88-8004B04232F3}"/>
+    <workbookView xWindow="900" yWindow="1820" windowWidth="27640" windowHeight="16940" xr2:uid="{54D7949B-B9B2-C347-8E88-8004B04232F3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -99,12 +99,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -119,9 +125,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -49014,7 +49022,7 @@
       </c>
     </row>
     <row r="1283" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1283" s="1">
+      <c r="A1283" s="2">
         <v>44747</v>
       </c>
       <c r="B1283">
@@ -49032,7 +49040,7 @@
       <c r="F1283">
         <v>14.7</v>
       </c>
-      <c r="G1283">
+      <c r="G1283" s="3">
         <v>28.1</v>
       </c>
       <c r="H1283">
@@ -49052,7 +49060,7 @@
       </c>
     </row>
     <row r="1284" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1284" s="1">
+      <c r="A1284" s="2">
         <v>44748</v>
       </c>
       <c r="B1284">
@@ -49070,7 +49078,7 @@
       <c r="F1284">
         <v>14</v>
       </c>
-      <c r="G1284">
+      <c r="G1284" s="3">
         <v>0</v>
       </c>
       <c r="H1284">
@@ -49090,7 +49098,7 @@
       </c>
     </row>
     <row r="1285" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1285" s="1">
+      <c r="A1285" s="2">
         <v>44749</v>
       </c>
       <c r="B1285">
@@ -49108,7 +49116,7 @@
       <c r="F1285">
         <v>13.5</v>
       </c>
-      <c r="G1285">
+      <c r="G1285" s="3">
         <v>2.2999999999999998</v>
       </c>
       <c r="H1285">
@@ -49128,7 +49136,7 @@
       </c>
     </row>
     <row r="1286" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1286" s="1">
+      <c r="A1286" s="2">
         <v>44750</v>
       </c>
       <c r="B1286">
@@ -49146,7 +49154,7 @@
       <c r="F1286">
         <v>13.5</v>
       </c>
-      <c r="G1286">
+      <c r="G1286" s="3">
         <v>0.5</v>
       </c>
       <c r="H1286">
@@ -49166,7 +49174,7 @@
       </c>
     </row>
     <row r="1287" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1287" s="1">
+      <c r="A1287" s="2">
         <v>44751</v>
       </c>
       <c r="B1287">
@@ -49184,7 +49192,7 @@
       <c r="F1287">
         <v>13.3</v>
       </c>
-      <c r="G1287">
+      <c r="G1287" s="3">
         <v>6.1</v>
       </c>
       <c r="H1287">
@@ -49204,7 +49212,7 @@
       </c>
     </row>
     <row r="1288" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1288" s="1">
+      <c r="A1288" s="2">
         <v>44752</v>
       </c>
       <c r="B1288">
@@ -49222,7 +49230,7 @@
       <c r="F1288">
         <v>13.1</v>
       </c>
-      <c r="G1288">
+      <c r="G1288" s="3">
         <v>21.4</v>
       </c>
       <c r="H1288">
@@ -49242,7 +49250,7 @@
       </c>
     </row>
     <row r="1289" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1289" s="1">
+      <c r="A1289" s="2">
         <v>44753</v>
       </c>
       <c r="B1289">
@@ -49260,7 +49268,7 @@
       <c r="F1289">
         <v>13.4</v>
       </c>
-      <c r="G1289">
+      <c r="G1289" s="3">
         <v>0</v>
       </c>
       <c r="H1289">
@@ -49280,7 +49288,7 @@
       </c>
     </row>
     <row r="1290" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1290" s="1">
+      <c r="A1290" s="2">
         <v>44754</v>
       </c>
       <c r="B1290">
@@ -49298,7 +49306,7 @@
       <c r="F1290">
         <v>13.7</v>
       </c>
-      <c r="G1290">
+      <c r="G1290" s="3">
         <v>0</v>
       </c>
       <c r="H1290">
@@ -49318,7 +49326,7 @@
       </c>
     </row>
     <row r="1291" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1291" s="1">
+      <c r="A1291" s="2">
         <v>44755</v>
       </c>
       <c r="B1291">
@@ -49336,7 +49344,7 @@
       <c r="F1291">
         <v>14</v>
       </c>
-      <c r="G1291">
+      <c r="G1291" s="3">
         <v>0</v>
       </c>
       <c r="H1291">
@@ -49356,7 +49364,7 @@
       </c>
     </row>
     <row r="1292" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1292" s="1">
+      <c r="A1292" s="2">
         <v>44756</v>
       </c>
       <c r="B1292">
@@ -49374,7 +49382,7 @@
       <c r="F1292">
         <v>14.2</v>
       </c>
-      <c r="G1292">
+      <c r="G1292" s="3">
         <v>33.1</v>
       </c>
       <c r="H1292">
@@ -49394,7 +49402,7 @@
       </c>
     </row>
     <row r="1293" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A1293" s="1">
+      <c r="A1293" s="2">
         <v>44757</v>
       </c>
       <c r="B1293">
@@ -49412,7 +49420,7 @@
       <c r="F1293">
         <v>14</v>
       </c>
-      <c r="G1293">
+      <c r="G1293" s="3">
         <v>4.7</v>
       </c>
       <c r="H1293">
